--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119950503</v>
+        <v>119950415</v>
       </c>
       <c r="B2" t="n">
-        <v>57679</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479505</v>
+        <v>479499</v>
       </c>
       <c r="R2" t="n">
-        <v>6503631</v>
+        <v>6503556</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119949606</v>
+        <v>119950503</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57679</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,35 +818,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -860,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479497</v>
+        <v>479505</v>
       </c>
       <c r="R3" t="n">
-        <v>6503649</v>
+        <v>6503631</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119950415</v>
+        <v>119949606</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479499</v>
+        <v>479497</v>
       </c>
       <c r="R4" t="n">
-        <v>6503556</v>
+        <v>6503649</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119950503</v>
+        <v>119949606</v>
       </c>
       <c r="B3" t="n">
-        <v>57679</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,40 +818,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -865,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479505</v>
+        <v>479497</v>
       </c>
       <c r="R3" t="n">
-        <v>6503631</v>
+        <v>6503649</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119949606</v>
+        <v>119950503</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>57679</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,35 +949,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -991,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479497</v>
+        <v>479505</v>
       </c>
       <c r="R4" t="n">
-        <v>6503649</v>
+        <v>6503631</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1041,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119950415</v>
+        <v>119949606</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479499</v>
+        <v>479497</v>
       </c>
       <c r="R2" t="n">
-        <v>6503556</v>
+        <v>6503649</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119949606</v>
+        <v>119950415</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -841,7 +841,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479497</v>
+        <v>479499</v>
       </c>
       <c r="R3" t="n">
-        <v>6503649</v>
+        <v>6503556</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119949606</v>
+        <v>119950503</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479497</v>
+        <v>479505</v>
       </c>
       <c r="R2" t="n">
-        <v>6503649</v>
+        <v>6503631</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,7 +809,7 @@
         <v>119950415</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119950503</v>
+        <v>119949606</v>
       </c>
       <c r="B4" t="n">
-        <v>57679</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,40 +949,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -996,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479505</v>
+        <v>479497</v>
       </c>
       <c r="R4" t="n">
-        <v>6503631</v>
+        <v>6503649</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119950503</v>
+        <v>119950415</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479505</v>
+        <v>479499</v>
       </c>
       <c r="R2" t="n">
-        <v>6503631</v>
+        <v>6503556</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119950415</v>
+        <v>119950503</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,35 +818,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -860,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479499</v>
+        <v>479505</v>
       </c>
       <c r="R3" t="n">
-        <v>6503556</v>
+        <v>6503631</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119950415</v>
+        <v>119950503</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479499</v>
+        <v>479505</v>
       </c>
       <c r="R2" t="n">
-        <v>6503556</v>
+        <v>6503631</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119950503</v>
+        <v>119949606</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,40 +818,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -865,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479505</v>
+        <v>479497</v>
       </c>
       <c r="R3" t="n">
-        <v>6503631</v>
+        <v>6503649</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119949606</v>
+        <v>119950415</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479497</v>
+        <v>479499</v>
       </c>
       <c r="R4" t="n">
-        <v>6503649</v>
+        <v>6503556</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119950503</v>
+        <v>119950415</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479505</v>
+        <v>479499</v>
       </c>
       <c r="R2" t="n">
-        <v>6503631</v>
+        <v>6503556</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119949606</v>
+        <v>119950503</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,35 +818,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -860,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479497</v>
+        <v>479505</v>
       </c>
       <c r="R3" t="n">
-        <v>6503649</v>
+        <v>6503631</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +910,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119950415</v>
+        <v>119949606</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479499</v>
+        <v>479497</v>
       </c>
       <c r="R4" t="n">
-        <v>6503556</v>
+        <v>6503649</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119950415</v>
+        <v>119950503</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479499</v>
+        <v>479505</v>
       </c>
       <c r="R2" t="n">
-        <v>6503556</v>
+        <v>6503631</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119950503</v>
+        <v>119950415</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,40 +818,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -865,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479505</v>
+        <v>479499</v>
       </c>
       <c r="R3" t="n">
-        <v>6503631</v>
+        <v>6503556</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,7 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119950415</v>
+        <v>119949606</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -841,7 +841,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479499</v>
+        <v>479497</v>
       </c>
       <c r="R3" t="n">
-        <v>6503556</v>
+        <v>6503649</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
+          <t>Enstaka rosetter, en torkad blomställning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119949606</v>
+        <v>119950415</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479497</v>
+        <v>479499</v>
       </c>
       <c r="R4" t="n">
-        <v>6503649</v>
+        <v>6503556</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka rosetter, en torkad blomställning.</t>
+          <t>Flertal rosetter i mossan, fyra torkade blomstänglar. Östlig sluttning, 2/3 upp i branten.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124326743</v>
+        <v>124326742</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479534</v>
+        <v>479502</v>
       </c>
       <c r="R5" t="n">
-        <v>6503560</v>
+        <v>6503561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124326742</v>
+        <v>124326743</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479502</v>
+        <v>479534</v>
       </c>
       <c r="R6" t="n">
-        <v>6503561</v>
+        <v>6503560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -1068,7 +1068,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124326742</v>
+        <v>124326743</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479502</v>
+        <v>479534</v>
       </c>
       <c r="R5" t="n">
-        <v>6503561</v>
+        <v>6503560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124326743</v>
+        <v>124326742</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479534</v>
+        <v>479502</v>
       </c>
       <c r="R6" t="n">
-        <v>6503560</v>
+        <v>6503561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119950503</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,12 +804,7 @@
         <v>119949606</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,12 +930,7 @@
         <v>119950415</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124326743</v>
+        <v>124326741</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1112,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479534</v>
+        <v>479504</v>
       </c>
       <c r="R5" t="n">
-        <v>6503560</v>
+        <v>6503647</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1182,12 +1162,7 @@
         <v>124326742</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,6 +1262,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124326743</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bocksjö, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>479534</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6503560</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38204-2024 artfynd.xlsx
+++ b/artfynd/A 38204-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119950503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119949606</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119950415</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326741</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326742</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,8 +1398,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>